--- a/framework-pdfs/PFWP RACI.xlsx
+++ b/framework-pdfs/PFWP RACI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Martin/Documents/0 Punkfrog/06 Quality/Templates/13 Operations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAB58EBD-3870-B748-B343-72F737285597}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70ABD37D-5480-6A4C-B230-AA4EA93D6E98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-9860" yWindow="-27540" windowWidth="35140" windowHeight="27540" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -402,10 +402,6 @@
     <t>A clear framework for assigning roles and accountability.</t>
   </si>
   <si>
-    <t>PF/O-26:003
-2026-03-06 version 1.0.1</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">• Note that grouped data in Excel collapses </t>
     </r>
@@ -426,6 +422,10 @@
       </rPr>
       <t xml:space="preserve"> to it's heading. This is because Excel is a spreadsheet, and this function is used to hide detail and show the sum of a column. This means that section "Headings" are actually "Footings".</t>
     </r>
+  </si>
+  <si>
+    <t>PF/O-26:003
+2026-03-06 version 2.0.0</t>
   </si>
 </sst>
 </file>
@@ -1146,6 +1146,51 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" textRotation="90"/>
     </xf>
@@ -1186,51 +1231,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:6" s="48" customFormat="1" ht="42" customHeight="1">
@@ -1769,7 +1769,7 @@
     </row>
     <row r="15" spans="1:6" ht="38" customHeight="1">
       <c r="B15" s="49" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C15" s="49"/>
     </row>
@@ -1970,181 +1970,181 @@
       <c r="I1" s="2"/>
       <c r="N1" s="2"/>
       <c r="S1" s="2"/>
-      <c r="AE1" s="53" t="s">
+      <c r="AE1" s="68" t="s">
         <v>50</v>
       </c>
-      <c r="AF1" s="53"/>
-      <c r="AG1" s="53"/>
-      <c r="AH1" s="53"/>
-      <c r="AI1" s="53"/>
+      <c r="AF1" s="68"/>
+      <c r="AG1" s="68"/>
+      <c r="AH1" s="68"/>
+      <c r="AI1" s="68"/>
     </row>
     <row r="2" spans="1:35" s="12" customFormat="1" ht="17" customHeight="1">
-      <c r="B2" s="66" t="s">
+      <c r="B2" s="52" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="69" t="s">
+      <c r="C2" s="55" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="63" t="s">
+      <c r="D2" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="64"/>
-      <c r="F2" s="64"/>
-      <c r="G2" s="64"/>
-      <c r="H2" s="64"/>
-      <c r="I2" s="65"/>
-      <c r="J2" s="65"/>
-      <c r="K2" s="65"/>
-      <c r="L2" s="65"/>
-      <c r="M2" s="65"/>
-      <c r="N2" s="65"/>
-      <c r="O2" s="65"/>
-      <c r="P2" s="65"/>
-      <c r="Q2" s="65"/>
-      <c r="R2" s="65"/>
-      <c r="S2" s="65"/>
-      <c r="T2" s="65"/>
-      <c r="U2" s="65"/>
-      <c r="V2" s="65"/>
-      <c r="W2" s="65"/>
-      <c r="X2" s="65"/>
-      <c r="Y2" s="65"/>
-      <c r="Z2" s="65"/>
-      <c r="AA2" s="65"/>
-      <c r="AB2" s="65"/>
-      <c r="AC2" s="72" t="s">
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="80"/>
+      <c r="J2" s="80"/>
+      <c r="K2" s="80"/>
+      <c r="L2" s="80"/>
+      <c r="M2" s="80"/>
+      <c r="N2" s="80"/>
+      <c r="O2" s="80"/>
+      <c r="P2" s="80"/>
+      <c r="Q2" s="80"/>
+      <c r="R2" s="80"/>
+      <c r="S2" s="80"/>
+      <c r="T2" s="80"/>
+      <c r="U2" s="80"/>
+      <c r="V2" s="80"/>
+      <c r="W2" s="80"/>
+      <c r="X2" s="80"/>
+      <c r="Y2" s="80"/>
+      <c r="Z2" s="80"/>
+      <c r="AA2" s="80"/>
+      <c r="AB2" s="80"/>
+      <c r="AC2" s="58" t="s">
         <v>17</v>
       </c>
-      <c r="AE2" s="54" t="str">
+      <c r="AE2" s="69" t="str">
         <f>C39</f>
         <v>Accountable &amp; Responsible</v>
       </c>
-      <c r="AF2" s="54" t="str">
+      <c r="AF2" s="69" t="str">
         <f>C40</f>
         <v>Accountable</v>
       </c>
-      <c r="AG2" s="54" t="str">
+      <c r="AG2" s="69" t="str">
         <f>C41</f>
         <v>Responsible</v>
       </c>
-      <c r="AH2" s="54" t="str">
+      <c r="AH2" s="69" t="str">
         <f>C42</f>
         <v>must be Consulted</v>
       </c>
-      <c r="AI2" s="54" t="str">
+      <c r="AI2" s="69" t="str">
         <f>C43</f>
         <v>must be Informed</v>
       </c>
     </row>
     <row r="3" spans="1:35" s="12" customFormat="1" ht="17">
-      <c r="B3" s="67"/>
-      <c r="C3" s="70"/>
-      <c r="D3" s="77">
+      <c r="B3" s="53"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="63">
         <v>1</v>
       </c>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="74">
+      <c r="E3" s="61"/>
+      <c r="F3" s="61"/>
+      <c r="G3" s="61"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="60">
         <v>2</v>
       </c>
-      <c r="J3" s="75"/>
-      <c r="K3" s="75"/>
-      <c r="L3" s="75"/>
-      <c r="M3" s="75"/>
-      <c r="N3" s="74">
+      <c r="J3" s="61"/>
+      <c r="K3" s="61"/>
+      <c r="L3" s="61"/>
+      <c r="M3" s="61"/>
+      <c r="N3" s="60">
         <v>3</v>
       </c>
-      <c r="O3" s="75"/>
-      <c r="P3" s="75"/>
-      <c r="Q3" s="75"/>
-      <c r="R3" s="76"/>
-      <c r="S3" s="75">
+      <c r="O3" s="61"/>
+      <c r="P3" s="61"/>
+      <c r="Q3" s="61"/>
+      <c r="R3" s="62"/>
+      <c r="S3" s="61">
         <v>4</v>
       </c>
-      <c r="T3" s="75"/>
-      <c r="U3" s="75"/>
-      <c r="V3" s="75"/>
-      <c r="W3" s="76"/>
-      <c r="X3" s="74">
+      <c r="T3" s="61"/>
+      <c r="U3" s="61"/>
+      <c r="V3" s="61"/>
+      <c r="W3" s="62"/>
+      <c r="X3" s="60">
         <v>5</v>
       </c>
-      <c r="Y3" s="75"/>
-      <c r="Z3" s="75"/>
-      <c r="AA3" s="75"/>
-      <c r="AB3" s="76"/>
-      <c r="AC3" s="73"/>
-      <c r="AE3" s="55"/>
-      <c r="AF3" s="55" t="s">
-        <v>0</v>
-      </c>
-      <c r="AG3" s="55" t="s">
-        <v>0</v>
-      </c>
-      <c r="AH3" s="55" t="s">
-        <v>0</v>
-      </c>
-      <c r="AI3" s="55" t="s">
+      <c r="Y3" s="61"/>
+      <c r="Z3" s="61"/>
+      <c r="AA3" s="61"/>
+      <c r="AB3" s="62"/>
+      <c r="AC3" s="59"/>
+      <c r="AE3" s="70"/>
+      <c r="AF3" s="70" t="s">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="70" t="s">
+        <v>0</v>
+      </c>
+      <c r="AH3" s="70" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI3" s="70" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:35" s="12" customFormat="1" ht="31" customHeight="1">
-      <c r="B4" s="67"/>
-      <c r="C4" s="70"/>
-      <c r="D4" s="78" t="s">
+      <c r="B4" s="53"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="79"/>
-      <c r="F4" s="79"/>
-      <c r="G4" s="79"/>
-      <c r="H4" s="80"/>
-      <c r="I4" s="78" t="s">
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="66"/>
+      <c r="I4" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="79"/>
-      <c r="K4" s="79"/>
-      <c r="L4" s="79"/>
-      <c r="M4" s="80"/>
-      <c r="N4" s="78" t="s">
+      <c r="J4" s="65"/>
+      <c r="K4" s="65"/>
+      <c r="L4" s="65"/>
+      <c r="M4" s="66"/>
+      <c r="N4" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="O4" s="79"/>
-      <c r="P4" s="79"/>
-      <c r="Q4" s="79"/>
-      <c r="R4" s="80"/>
-      <c r="S4" s="78" t="s">
+      <c r="O4" s="65"/>
+      <c r="P4" s="65"/>
+      <c r="Q4" s="65"/>
+      <c r="R4" s="66"/>
+      <c r="S4" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="T4" s="79"/>
-      <c r="U4" s="79"/>
-      <c r="V4" s="79"/>
-      <c r="W4" s="80"/>
-      <c r="X4" s="78" t="s">
+      <c r="T4" s="65"/>
+      <c r="U4" s="65"/>
+      <c r="V4" s="65"/>
+      <c r="W4" s="66"/>
+      <c r="X4" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="Y4" s="79"/>
-      <c r="Z4" s="79"/>
-      <c r="AA4" s="79"/>
-      <c r="AB4" s="80"/>
-      <c r="AC4" s="73"/>
-      <c r="AE4" s="55"/>
-      <c r="AF4" s="55" t="s">
-        <v>0</v>
-      </c>
-      <c r="AG4" s="55" t="s">
-        <v>0</v>
-      </c>
-      <c r="AH4" s="55" t="s">
-        <v>0</v>
-      </c>
-      <c r="AI4" s="55" t="s">
+      <c r="Y4" s="65"/>
+      <c r="Z4" s="65"/>
+      <c r="AA4" s="65"/>
+      <c r="AB4" s="66"/>
+      <c r="AC4" s="59"/>
+      <c r="AE4" s="70"/>
+      <c r="AF4" s="70" t="s">
+        <v>0</v>
+      </c>
+      <c r="AG4" s="70" t="s">
+        <v>0</v>
+      </c>
+      <c r="AH4" s="70" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI4" s="70" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:35" s="12" customFormat="1" ht="92" customHeight="1" thickBot="1">
-      <c r="B5" s="68"/>
-      <c r="C5" s="71"/>
+      <c r="B5" s="54"/>
+      <c r="C5" s="57"/>
       <c r="D5" s="38" t="s">
         <v>1</v>
       </c>
@@ -2220,18 +2220,18 @@
       <c r="AB5" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="AC5" s="73"/>
-      <c r="AE5" s="56"/>
-      <c r="AF5" s="56" t="s">
-        <v>0</v>
-      </c>
-      <c r="AG5" s="56" t="s">
-        <v>0</v>
-      </c>
-      <c r="AH5" s="56" t="s">
-        <v>0</v>
-      </c>
-      <c r="AI5" s="56" t="s">
+      <c r="AC5" s="59"/>
+      <c r="AE5" s="71"/>
+      <c r="AF5" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="AG5" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="AH5" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI5" s="71" t="s">
         <v>0</v>
       </c>
     </row>
@@ -2474,34 +2474,34 @@
       <c r="C10" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="57" t="str">
+      <c r="D10" s="72" t="str">
         <f>C10</f>
         <v>MAJOR TASK</v>
       </c>
-      <c r="E10" s="58"/>
-      <c r="F10" s="58"/>
-      <c r="G10" s="58"/>
-      <c r="H10" s="58"/>
-      <c r="I10" s="58"/>
-      <c r="J10" s="58"/>
-      <c r="K10" s="58"/>
-      <c r="L10" s="58"/>
-      <c r="M10" s="58"/>
-      <c r="N10" s="58"/>
-      <c r="O10" s="58"/>
-      <c r="P10" s="58"/>
-      <c r="Q10" s="58"/>
-      <c r="R10" s="58"/>
-      <c r="S10" s="58"/>
-      <c r="T10" s="58"/>
-      <c r="U10" s="58"/>
-      <c r="V10" s="58"/>
-      <c r="W10" s="58"/>
-      <c r="X10" s="58"/>
-      <c r="Y10" s="58"/>
-      <c r="Z10" s="58"/>
-      <c r="AA10" s="58"/>
-      <c r="AB10" s="59"/>
+      <c r="E10" s="73"/>
+      <c r="F10" s="73"/>
+      <c r="G10" s="73"/>
+      <c r="H10" s="73"/>
+      <c r="I10" s="73"/>
+      <c r="J10" s="73"/>
+      <c r="K10" s="73"/>
+      <c r="L10" s="73"/>
+      <c r="M10" s="73"/>
+      <c r="N10" s="73"/>
+      <c r="O10" s="73"/>
+      <c r="P10" s="73"/>
+      <c r="Q10" s="73"/>
+      <c r="R10" s="73"/>
+      <c r="S10" s="73"/>
+      <c r="T10" s="73"/>
+      <c r="U10" s="73"/>
+      <c r="V10" s="73"/>
+      <c r="W10" s="73"/>
+      <c r="X10" s="73"/>
+      <c r="Y10" s="73"/>
+      <c r="Z10" s="73"/>
+      <c r="AA10" s="73"/>
+      <c r="AB10" s="74"/>
       <c r="AC10" s="44"/>
       <c r="AE10" s="30"/>
       <c r="AF10" s="30"/>
@@ -2736,34 +2736,34 @@
       <c r="C15" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="57" t="str">
+      <c r="D15" s="72" t="str">
         <f>C15</f>
         <v>MAJOR TASK</v>
       </c>
-      <c r="E15" s="58"/>
-      <c r="F15" s="58"/>
-      <c r="G15" s="58"/>
-      <c r="H15" s="58"/>
-      <c r="I15" s="58"/>
-      <c r="J15" s="58"/>
-      <c r="K15" s="58"/>
-      <c r="L15" s="58"/>
-      <c r="M15" s="58"/>
-      <c r="N15" s="58"/>
-      <c r="O15" s="58"/>
-      <c r="P15" s="58"/>
-      <c r="Q15" s="58"/>
-      <c r="R15" s="58"/>
-      <c r="S15" s="58"/>
-      <c r="T15" s="58"/>
-      <c r="U15" s="58"/>
-      <c r="V15" s="58"/>
-      <c r="W15" s="58"/>
-      <c r="X15" s="58"/>
-      <c r="Y15" s="58"/>
-      <c r="Z15" s="58"/>
-      <c r="AA15" s="58"/>
-      <c r="AB15" s="59"/>
+      <c r="E15" s="73"/>
+      <c r="F15" s="73"/>
+      <c r="G15" s="73"/>
+      <c r="H15" s="73"/>
+      <c r="I15" s="73"/>
+      <c r="J15" s="73"/>
+      <c r="K15" s="73"/>
+      <c r="L15" s="73"/>
+      <c r="M15" s="73"/>
+      <c r="N15" s="73"/>
+      <c r="O15" s="73"/>
+      <c r="P15" s="73"/>
+      <c r="Q15" s="73"/>
+      <c r="R15" s="73"/>
+      <c r="S15" s="73"/>
+      <c r="T15" s="73"/>
+      <c r="U15" s="73"/>
+      <c r="V15" s="73"/>
+      <c r="W15" s="73"/>
+      <c r="X15" s="73"/>
+      <c r="Y15" s="73"/>
+      <c r="Z15" s="73"/>
+      <c r="AA15" s="73"/>
+      <c r="AB15" s="74"/>
       <c r="AC15" s="44"/>
       <c r="AE15" s="30"/>
       <c r="AF15" s="30"/>
@@ -2998,34 +2998,34 @@
       <c r="C20" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="D20" s="57" t="str">
+      <c r="D20" s="72" t="str">
         <f>C20</f>
         <v>MAJOR TASK</v>
       </c>
-      <c r="E20" s="58"/>
-      <c r="F20" s="58"/>
-      <c r="G20" s="58"/>
-      <c r="H20" s="58"/>
-      <c r="I20" s="58"/>
-      <c r="J20" s="58"/>
-      <c r="K20" s="58"/>
-      <c r="L20" s="58"/>
-      <c r="M20" s="58"/>
-      <c r="N20" s="58"/>
-      <c r="O20" s="58"/>
-      <c r="P20" s="58"/>
-      <c r="Q20" s="58"/>
-      <c r="R20" s="58"/>
-      <c r="S20" s="58"/>
-      <c r="T20" s="58"/>
-      <c r="U20" s="58"/>
-      <c r="V20" s="58"/>
-      <c r="W20" s="58"/>
-      <c r="X20" s="58"/>
-      <c r="Y20" s="58"/>
-      <c r="Z20" s="58"/>
-      <c r="AA20" s="58"/>
-      <c r="AB20" s="59"/>
+      <c r="E20" s="73"/>
+      <c r="F20" s="73"/>
+      <c r="G20" s="73"/>
+      <c r="H20" s="73"/>
+      <c r="I20" s="73"/>
+      <c r="J20" s="73"/>
+      <c r="K20" s="73"/>
+      <c r="L20" s="73"/>
+      <c r="M20" s="73"/>
+      <c r="N20" s="73"/>
+      <c r="O20" s="73"/>
+      <c r="P20" s="73"/>
+      <c r="Q20" s="73"/>
+      <c r="R20" s="73"/>
+      <c r="S20" s="73"/>
+      <c r="T20" s="73"/>
+      <c r="U20" s="73"/>
+      <c r="V20" s="73"/>
+      <c r="W20" s="73"/>
+      <c r="X20" s="73"/>
+      <c r="Y20" s="73"/>
+      <c r="Z20" s="73"/>
+      <c r="AA20" s="73"/>
+      <c r="AB20" s="74"/>
       <c r="AC20" s="44"/>
       <c r="AE20" s="30"/>
       <c r="AF20" s="30"/>
@@ -3040,34 +3040,34 @@
       <c r="C21" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="D21" s="60" t="str">
+      <c r="D21" s="75" t="str">
         <f>C21</f>
         <v>SUB-PROJECT</v>
       </c>
-      <c r="E21" s="61"/>
-      <c r="F21" s="61"/>
-      <c r="G21" s="61"/>
-      <c r="H21" s="61"/>
-      <c r="I21" s="61"/>
-      <c r="J21" s="61"/>
-      <c r="K21" s="61"/>
-      <c r="L21" s="61"/>
-      <c r="M21" s="61"/>
-      <c r="N21" s="61"/>
-      <c r="O21" s="61"/>
-      <c r="P21" s="61"/>
-      <c r="Q21" s="61"/>
-      <c r="R21" s="61"/>
-      <c r="S21" s="61"/>
-      <c r="T21" s="61"/>
-      <c r="U21" s="61"/>
-      <c r="V21" s="61"/>
-      <c r="W21" s="61"/>
-      <c r="X21" s="61"/>
-      <c r="Y21" s="61"/>
-      <c r="Z21" s="61"/>
-      <c r="AA21" s="61"/>
-      <c r="AB21" s="62"/>
+      <c r="E21" s="76"/>
+      <c r="F21" s="76"/>
+      <c r="G21" s="76"/>
+      <c r="H21" s="76"/>
+      <c r="I21" s="76"/>
+      <c r="J21" s="76"/>
+      <c r="K21" s="76"/>
+      <c r="L21" s="76"/>
+      <c r="M21" s="76"/>
+      <c r="N21" s="76"/>
+      <c r="O21" s="76"/>
+      <c r="P21" s="76"/>
+      <c r="Q21" s="76"/>
+      <c r="R21" s="76"/>
+      <c r="S21" s="76"/>
+      <c r="T21" s="76"/>
+      <c r="U21" s="76"/>
+      <c r="V21" s="76"/>
+      <c r="W21" s="76"/>
+      <c r="X21" s="76"/>
+      <c r="Y21" s="76"/>
+      <c r="Z21" s="76"/>
+      <c r="AA21" s="76"/>
+      <c r="AB21" s="77"/>
       <c r="AC21" s="41"/>
       <c r="AE21" s="31"/>
       <c r="AF21" s="31"/>
@@ -3302,34 +3302,34 @@
       <c r="C26" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="D26" s="57" t="str">
+      <c r="D26" s="72" t="str">
         <f>C26</f>
         <v>MAJOR TASK</v>
       </c>
-      <c r="E26" s="58"/>
-      <c r="F26" s="58"/>
-      <c r="G26" s="58"/>
-      <c r="H26" s="58"/>
-      <c r="I26" s="58"/>
-      <c r="J26" s="58"/>
-      <c r="K26" s="58"/>
-      <c r="L26" s="58"/>
-      <c r="M26" s="58"/>
-      <c r="N26" s="58"/>
-      <c r="O26" s="58"/>
-      <c r="P26" s="58"/>
-      <c r="Q26" s="58"/>
-      <c r="R26" s="58"/>
-      <c r="S26" s="58"/>
-      <c r="T26" s="58"/>
-      <c r="U26" s="58"/>
-      <c r="V26" s="58"/>
-      <c r="W26" s="58"/>
-      <c r="X26" s="58"/>
-      <c r="Y26" s="58"/>
-      <c r="Z26" s="58"/>
-      <c r="AA26" s="58"/>
-      <c r="AB26" s="59"/>
+      <c r="E26" s="73"/>
+      <c r="F26" s="73"/>
+      <c r="G26" s="73"/>
+      <c r="H26" s="73"/>
+      <c r="I26" s="73"/>
+      <c r="J26" s="73"/>
+      <c r="K26" s="73"/>
+      <c r="L26" s="73"/>
+      <c r="M26" s="73"/>
+      <c r="N26" s="73"/>
+      <c r="O26" s="73"/>
+      <c r="P26" s="73"/>
+      <c r="Q26" s="73"/>
+      <c r="R26" s="73"/>
+      <c r="S26" s="73"/>
+      <c r="T26" s="73"/>
+      <c r="U26" s="73"/>
+      <c r="V26" s="73"/>
+      <c r="W26" s="73"/>
+      <c r="X26" s="73"/>
+      <c r="Y26" s="73"/>
+      <c r="Z26" s="73"/>
+      <c r="AA26" s="73"/>
+      <c r="AB26" s="74"/>
       <c r="AC26" s="44"/>
       <c r="AE26" s="30"/>
       <c r="AF26" s="30"/>
@@ -3564,34 +3564,34 @@
       <c r="C31" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="D31" s="57" t="str">
+      <c r="D31" s="72" t="str">
         <f>C31</f>
         <v>MAJOR TASK</v>
       </c>
-      <c r="E31" s="58"/>
-      <c r="F31" s="58"/>
-      <c r="G31" s="58"/>
-      <c r="H31" s="58"/>
-      <c r="I31" s="58"/>
-      <c r="J31" s="58"/>
-      <c r="K31" s="58"/>
-      <c r="L31" s="58"/>
-      <c r="M31" s="58"/>
-      <c r="N31" s="58"/>
-      <c r="O31" s="58"/>
-      <c r="P31" s="58"/>
-      <c r="Q31" s="58"/>
-      <c r="R31" s="58"/>
-      <c r="S31" s="58"/>
-      <c r="T31" s="58"/>
-      <c r="U31" s="58"/>
-      <c r="V31" s="58"/>
-      <c r="W31" s="58"/>
-      <c r="X31" s="58"/>
-      <c r="Y31" s="58"/>
-      <c r="Z31" s="58"/>
-      <c r="AA31" s="58"/>
-      <c r="AB31" s="59"/>
+      <c r="E31" s="73"/>
+      <c r="F31" s="73"/>
+      <c r="G31" s="73"/>
+      <c r="H31" s="73"/>
+      <c r="I31" s="73"/>
+      <c r="J31" s="73"/>
+      <c r="K31" s="73"/>
+      <c r="L31" s="73"/>
+      <c r="M31" s="73"/>
+      <c r="N31" s="73"/>
+      <c r="O31" s="73"/>
+      <c r="P31" s="73"/>
+      <c r="Q31" s="73"/>
+      <c r="R31" s="73"/>
+      <c r="S31" s="73"/>
+      <c r="T31" s="73"/>
+      <c r="U31" s="73"/>
+      <c r="V31" s="73"/>
+      <c r="W31" s="73"/>
+      <c r="X31" s="73"/>
+      <c r="Y31" s="73"/>
+      <c r="Z31" s="73"/>
+      <c r="AA31" s="73"/>
+      <c r="AB31" s="74"/>
       <c r="AC31" s="44"/>
       <c r="AE31" s="30"/>
       <c r="AF31" s="30"/>
@@ -3826,34 +3826,34 @@
       <c r="C36" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="D36" s="57" t="str">
+      <c r="D36" s="72" t="str">
         <f>C36</f>
         <v>MAJOR TASK</v>
       </c>
-      <c r="E36" s="58"/>
-      <c r="F36" s="58"/>
-      <c r="G36" s="58"/>
-      <c r="H36" s="58"/>
-      <c r="I36" s="58"/>
-      <c r="J36" s="58"/>
-      <c r="K36" s="58"/>
-      <c r="L36" s="58"/>
-      <c r="M36" s="58"/>
-      <c r="N36" s="58"/>
-      <c r="O36" s="58"/>
-      <c r="P36" s="58"/>
-      <c r="Q36" s="58"/>
-      <c r="R36" s="58"/>
-      <c r="S36" s="58"/>
-      <c r="T36" s="58"/>
-      <c r="U36" s="58"/>
-      <c r="V36" s="58"/>
-      <c r="W36" s="58"/>
-      <c r="X36" s="58"/>
-      <c r="Y36" s="58"/>
-      <c r="Z36" s="58"/>
-      <c r="AA36" s="58"/>
-      <c r="AB36" s="59"/>
+      <c r="E36" s="73"/>
+      <c r="F36" s="73"/>
+      <c r="G36" s="73"/>
+      <c r="H36" s="73"/>
+      <c r="I36" s="73"/>
+      <c r="J36" s="73"/>
+      <c r="K36" s="73"/>
+      <c r="L36" s="73"/>
+      <c r="M36" s="73"/>
+      <c r="N36" s="73"/>
+      <c r="O36" s="73"/>
+      <c r="P36" s="73"/>
+      <c r="Q36" s="73"/>
+      <c r="R36" s="73"/>
+      <c r="S36" s="73"/>
+      <c r="T36" s="73"/>
+      <c r="U36" s="73"/>
+      <c r="V36" s="73"/>
+      <c r="W36" s="73"/>
+      <c r="X36" s="73"/>
+      <c r="Y36" s="73"/>
+      <c r="Z36" s="73"/>
+      <c r="AA36" s="73"/>
+      <c r="AB36" s="74"/>
       <c r="AC36" s="44"/>
     </row>
     <row r="37" spans="1:35" s="12" customFormat="1" ht="18">
@@ -3863,41 +3863,41 @@
       <c r="C37" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="D37" s="60" t="str">
+      <c r="D37" s="75" t="str">
         <f>C37</f>
         <v>SUB-PROJECT</v>
       </c>
-      <c r="E37" s="61"/>
-      <c r="F37" s="61"/>
-      <c r="G37" s="61"/>
-      <c r="H37" s="61"/>
-      <c r="I37" s="61"/>
-      <c r="J37" s="61"/>
-      <c r="K37" s="61"/>
-      <c r="L37" s="61"/>
-      <c r="M37" s="61"/>
-      <c r="N37" s="61"/>
-      <c r="O37" s="61"/>
-      <c r="P37" s="61"/>
-      <c r="Q37" s="61"/>
-      <c r="R37" s="61"/>
-      <c r="S37" s="61"/>
-      <c r="T37" s="61"/>
-      <c r="U37" s="61"/>
-      <c r="V37" s="61"/>
-      <c r="W37" s="61"/>
-      <c r="X37" s="61"/>
-      <c r="Y37" s="61"/>
-      <c r="Z37" s="61"/>
-      <c r="AA37" s="61"/>
-      <c r="AB37" s="62"/>
+      <c r="E37" s="76"/>
+      <c r="F37" s="76"/>
+      <c r="G37" s="76"/>
+      <c r="H37" s="76"/>
+      <c r="I37" s="76"/>
+      <c r="J37" s="76"/>
+      <c r="K37" s="76"/>
+      <c r="L37" s="76"/>
+      <c r="M37" s="76"/>
+      <c r="N37" s="76"/>
+      <c r="O37" s="76"/>
+      <c r="P37" s="76"/>
+      <c r="Q37" s="76"/>
+      <c r="R37" s="76"/>
+      <c r="S37" s="76"/>
+      <c r="T37" s="76"/>
+      <c r="U37" s="76"/>
+      <c r="V37" s="76"/>
+      <c r="W37" s="76"/>
+      <c r="X37" s="76"/>
+      <c r="Y37" s="76"/>
+      <c r="Z37" s="76"/>
+      <c r="AA37" s="76"/>
+      <c r="AB37" s="77"/>
       <c r="AC37" s="41"/>
     </row>
     <row r="38" spans="1:35" s="18" customFormat="1" ht="18" thickBot="1">
       <c r="C38" s="19"/>
     </row>
     <row r="39" spans="1:35" s="18" customFormat="1" ht="15" customHeight="1">
-      <c r="B39" s="52" t="s">
+      <c r="B39" s="67" t="s">
         <v>50</v>
       </c>
       <c r="C39" s="21" t="s">
@@ -4005,7 +4005,7 @@
       </c>
     </row>
     <row r="40" spans="1:35" s="18" customFormat="1" ht="15" customHeight="1">
-      <c r="B40" s="52"/>
+      <c r="B40" s="67"/>
       <c r="C40" s="24" t="s">
         <v>52</v>
       </c>
@@ -4111,7 +4111,7 @@
       </c>
     </row>
     <row r="41" spans="1:35" s="18" customFormat="1" ht="15" customHeight="1">
-      <c r="B41" s="52"/>
+      <c r="B41" s="67"/>
       <c r="C41" s="24" t="s">
         <v>53</v>
       </c>
@@ -4217,7 +4217,7 @@
       </c>
     </row>
     <row r="42" spans="1:35" s="18" customFormat="1" ht="15" customHeight="1">
-      <c r="B42" s="52"/>
+      <c r="B42" s="67"/>
       <c r="C42" s="24" t="s">
         <v>54</v>
       </c>
@@ -4323,7 +4323,7 @@
       </c>
     </row>
     <row r="43" spans="1:35" s="18" customFormat="1" ht="15" customHeight="1" thickBot="1">
-      <c r="B43" s="52"/>
+      <c r="B43" s="67"/>
       <c r="C43" s="27" t="s">
         <v>55</v>
       </c>
@@ -4430,19 +4430,6 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B2:B5"/>
-    <mergeCell ref="C2:C5"/>
-    <mergeCell ref="AC2:AC5"/>
-    <mergeCell ref="X3:AB3"/>
-    <mergeCell ref="D3:H3"/>
-    <mergeCell ref="I3:M3"/>
-    <mergeCell ref="N3:R3"/>
-    <mergeCell ref="S3:W3"/>
-    <mergeCell ref="D4:H4"/>
-    <mergeCell ref="I4:M4"/>
-    <mergeCell ref="N4:R4"/>
-    <mergeCell ref="S4:W4"/>
-    <mergeCell ref="X4:AB4"/>
     <mergeCell ref="B39:B43"/>
     <mergeCell ref="AE1:AI1"/>
     <mergeCell ref="AE2:AE5"/>
@@ -4459,6 +4446,19 @@
     <mergeCell ref="D36:AB36"/>
     <mergeCell ref="D21:AB21"/>
     <mergeCell ref="D2:AB2"/>
+    <mergeCell ref="B2:B5"/>
+    <mergeCell ref="C2:C5"/>
+    <mergeCell ref="AC2:AC5"/>
+    <mergeCell ref="X3:AB3"/>
+    <mergeCell ref="D3:H3"/>
+    <mergeCell ref="I3:M3"/>
+    <mergeCell ref="N3:R3"/>
+    <mergeCell ref="S3:W3"/>
+    <mergeCell ref="D4:H4"/>
+    <mergeCell ref="I4:M4"/>
+    <mergeCell ref="N4:R4"/>
+    <mergeCell ref="S4:W4"/>
+    <mergeCell ref="X4:AB4"/>
   </mergeCells>
   <phoneticPr fontId="12" type="noConversion"/>
   <conditionalFormatting sqref="D6:AB9 D10 D11:AB14 D15 D16:AB19 AC20 D20:D21 D22:AB25 D26 D27:AB30 D31 D32:AB35 AC36 D36:D37">
